--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R12e4f1e7c94147c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8d51d97b0538435c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8d51d97b0538435c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb076ff2695234245"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb076ff2695234245"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3970747627e44285"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3970747627e44285"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rba6775583601478e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rba6775583601478e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb3f399a7aeb9454e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb3f399a7aeb9454e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0844fe3b070644db"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0844fe3b070644db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4ed20a96723e43e5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4ed20a96723e43e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf8220ea800e94ecb"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf8220ea800e94ecb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1cdd4cbf6f364a14"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1cdd4cbf6f364a14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0398e9dcd3a246e0"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0398e9dcd3a246e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra763521111eb47d0"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra763521111eb47d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0230a6dce22144af"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0230a6dce22144af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf4b2472afe4c4bd2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf4b2472afe4c4bd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf381f4dbe772403a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf381f4dbe772403a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2b3561543bc34dc1"/>
   </x:sheets>
 </x:workbook>
 </file>
